--- a/Bao_Gia_Mau.xlsx
+++ b/Bao_Gia_Mau.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Bao_Gia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Du-an-bao-gia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BECE328-FF90-4E44-9D36-3FC822B92D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2867E5-4E73-479A-A4B2-E2DB438E2E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,12 +40,6 @@
     <t>BÁO GIÁ</t>
   </si>
   <si>
-    <t>TÊN CÔNG TY
-Địa chỉ: .....................................................
-Điện thoại: .................................................
-Email: ........................................................</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Số BG: BG-2024-001</t>
   </si>
   <si>
@@ -243,6 +237,12 @@
   </si>
   <si>
     <t>Cảm ơn quý khách đã quan tâm! Mọi thắc mắc xin liên hệ hotline để được hỗ trợ.</t>
+  </si>
+  <si>
+    <t>TÊN CÔNG TY: …...............................................................................
+Địa chỉ:  ….......................................................................................
+Điện thoại: …..................................................................................
+Email:.............................................................................................</t>
   </si>
 </sst>
 </file>
@@ -252,7 +252,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +342,21 @@
     </font>
     <font>
       <sz val="8.5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF64748B"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -417,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -461,62 +476,66 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,12 +849,12 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25"/>
+      <c r="A1" s="15"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
@@ -844,39 +863,39 @@
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33" t="s">
+      <c r="A2" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35" t="s">
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="28"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="21" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="27" t="s">
-        <v>4</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
-      <c r="F3" s="21" t="s">
-        <v>5</v>
+      <c r="F3" s="29" t="s">
+        <v>4</v>
       </c>
       <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>6</v>
+      <c r="A5" s="26" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -886,12 +905,12 @@
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="23" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="18" t="s">
-        <v>8</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
@@ -899,12 +918,12 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="23" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="18" t="s">
-        <v>10</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -912,12 +931,12 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="23" t="s">
         <v>11</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="18" t="s">
-        <v>12</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
@@ -925,44 +944,44 @@
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="18" t="s">
-        <v>14</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>16</v>
       </c>
       <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -970,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
@@ -994,13 +1013,13 @@
         <v>2</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="7">
         <v>1</v>
@@ -1018,13 +1037,13 @@
         <v>3</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="4">
         <v>1</v>
@@ -1042,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="7">
         <v>1</v>
@@ -1066,13 +1085,13 @@
         <v>5</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="4">
         <v>1</v>
@@ -1090,13 +1109,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="D17" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="7">
         <v>1</v>
@@ -1114,13 +1133,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
@@ -1138,13 +1157,13 @@
         <v>8</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="D19" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="7">
         <v>1</v>
@@ -1162,13 +1181,13 @@
         <v>9</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
@@ -1186,13 +1205,13 @@
         <v>10</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="D21" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="7">
         <v>1</v>
@@ -1206,8 +1225,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>45</v>
+      <c r="A22" s="30" t="s">
+        <v>44</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1220,8 +1239,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>46</v>
+      <c r="A23" s="22" t="s">
+        <v>45</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -1236,8 +1255,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
-        <v>47</v>
+      <c r="A24" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -1251,8 +1270,8 @@
     </row>
     <row r="25" spans="1:7" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
-        <v>48</v>
+      <c r="A26" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -1262,114 +1281,114 @@
       <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-    </row>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="17" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-    </row>
-    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="B29" s="16"/>
+      <c r="C29" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17" t="s">
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-    </row>
-    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="B30" s="16"/>
+      <c r="C30" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
-        <v>57</v>
+      <c r="A32" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
-      <c r="E32" s="24" t="s">
-        <v>58</v>
+      <c r="E32" s="37" t="s">
+        <v>57</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="35" t="s">
         <v>60</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="19" t="s">
-        <v>61</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="26" t="s">
-        <v>65</v>
-      </c>
       <c r="F34" s="16"/>
-      <c r="G34" s="26" t="s">
-        <v>65</v>
+      <c r="G34" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
@@ -1381,8 +1400,8 @@
     </row>
     <row r="37" spans="1:7" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>68</v>
+      <c r="A38" s="36" t="s">
+        <v>67</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -1393,6 +1412,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E34:F36"/>
     <mergeCell ref="B35:D35"/>
@@ -1409,28 +1450,6 @@
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="G34:G36"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
